--- a/artfynd/A 63509-2021 artfynd.xlsx
+++ b/artfynd/A 63509-2021 artfynd.xlsx
@@ -529,7 +529,7 @@
       </c>
       <c r="W1" t="inlineStr">
         <is>
-          <t>Församling</t>
+          <t>Socken</t>
         </is>
       </c>
       <c r="X1" t="inlineStr">

--- a/artfynd/A 63509-2021 artfynd.xlsx
+++ b/artfynd/A 63509-2021 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY23"/>
+  <dimension ref="A1:AY25"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -675,50 +675,45 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>16895880</v>
+        <v>16895877</v>
       </c>
       <c r="B2" t="n">
-        <v>77668</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>97358</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>1249</v>
+        <v>53</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Norsk näverlav</t>
+          <t>Vedtrappmossa</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Platismatia norvegica</t>
+          <t>Crossocalyx hellerianus</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Lynge) W.L.Culb. &amp; C.F.Culb.</t>
+          <t>(Nees ex Lindenb.) Meyl.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
-          <t>Mosätern, N om, Jmt</t>
+          <t>Mosätern, Ö om, Jmt</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>448995.5635286387</v>
+        <v>449236</v>
       </c>
       <c r="R2" t="n">
-        <v>7171333.661069124</v>
+        <v>7171192</v>
       </c>
       <c r="S2" t="n">
         <v>25</v>
@@ -748,21 +743,11 @@
           <t>2014-07-01</t>
         </is>
       </c>
-      <c r="Z2" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA2" t="inlineStr">
         <is>
           <t>2014-07-01</t>
         </is>
       </c>
-      <c r="AB2" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AD2" t="b">
         <v>0</v>
       </c>
@@ -774,15 +759,15 @@
       </c>
       <c r="AI2" t="inlineStr">
         <is>
-          <t>luckig gammal fjällgranskog</t>
+          <t>luckig, björkrik fjällgranskog</t>
         </is>
       </c>
       <c r="AN2" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="AO2" t="inlineStr">
         <is>
-          <t>5 substratenheter # döda grangrenar på gamla granar</t>
+          <t>1 substratenheter # gammal granlåga, murken ved</t>
         </is>
       </c>
       <c r="AT2" t="inlineStr"/>
@@ -804,15 +789,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>16895869</v>
+        <v>120189967</v>
       </c>
       <c r="B3" t="n">
-        <v>77668</v>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>83298</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -820,37 +800,40 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>1249</v>
+        <v>492</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Norsk näverlav</t>
+          <t>Smalskaftslav</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Platismatia norvegica</t>
+          <t>Chaenotheca gracilenta</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Lynge) W.L.Culb. &amp; C.F.Culb.</t>
+          <t>(Ach.) J.Mattsson &amp; Middelb.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
+      <c r="J3" t="inlineStr"/>
+      <c r="K3" t="inlineStr"/>
+      <c r="N3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
-          <t>Övre Flohalsarna, ca 1,5 km Ö om Rörtjärnen, Jmt</t>
+          <t>Sandnäset, Jmt</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>449834.5079075008</v>
+        <v>449355</v>
       </c>
       <c r="R3" t="n">
-        <v>7170699.555016135</v>
+        <v>7169707</v>
       </c>
       <c r="S3" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
@@ -874,22 +857,12 @@
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>2014-07-01</t>
-        </is>
-      </c>
-      <c r="Z3" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2024-10-03</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>2014-07-01</t>
-        </is>
-      </c>
-      <c r="AB3" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2024-10-03</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -898,88 +871,70 @@
       <c r="AE3" t="b">
         <v>0</v>
       </c>
+      <c r="AF3" t="inlineStr"/>
       <c r="AG3" t="b">
         <v>0</v>
-      </c>
-      <c r="AI3" t="inlineStr">
-        <is>
-          <t>luckig, björkrik fjällgranskog, myrnära</t>
-        </is>
-      </c>
-      <c r="AN3" t="n">
-        <v>1</v>
-      </c>
-      <c r="AO3" t="inlineStr">
-        <is>
-          <t>1 substratenheter # stammen på gammal rönn</t>
-        </is>
       </c>
       <c r="AT3" t="inlineStr"/>
       <c r="AW3" t="inlineStr">
         <is>
-          <t>Magnus Andersson</t>
+          <t>Rashid Kadhim</t>
         </is>
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>Magnus Andersson</t>
-        </is>
-      </c>
-      <c r="AY3" t="inlineStr">
-        <is>
-          <t>SCA Skog Naturvärdesinventering</t>
-        </is>
-      </c>
+          <t>Rashid Kadhim</t>
+        </is>
+      </c>
+      <c r="AY3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>16895871</v>
+        <v>17225482</v>
       </c>
       <c r="B4" t="n">
-        <v>90074</v>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>78686</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>3298</v>
+        <v>498</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Trådticka</t>
+          <t>Liten sotlav</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Climacocystis borealis</t>
+          <t>Acolium karelicum</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Fr.) Kotl. &amp; Pouzar</t>
+          <t>(Vain.) M.Prieto &amp; Wedin</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
+      <c r="J4" t="inlineStr"/>
+      <c r="K4" t="inlineStr"/>
+      <c r="N4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
-          <t>Övre Flohalsarna, ca 1,5 km Ö om Rörtjärnen, Jmt</t>
+          <t>Mobäcken, Jmt</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>449401.762165326</v>
+        <v>448350</v>
       </c>
       <c r="R4" t="n">
-        <v>7170995.174812507</v>
+        <v>7169691</v>
       </c>
       <c r="S4" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>
@@ -1003,22 +958,17 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>2014-07-01</t>
-        </is>
-      </c>
-      <c r="Z4" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2014-07-18</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
         <is>
-          <t>2014-07-01</t>
-        </is>
-      </c>
-      <c r="AB4" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2014-07-18</t>
+        </is>
+      </c>
+      <c r="AC4" t="inlineStr">
+        <is>
+          <t>Artbestämd av Anders Nordin</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1027,12 +977,18 @@
       <c r="AE4" t="b">
         <v>0</v>
       </c>
+      <c r="AF4" t="inlineStr"/>
       <c r="AG4" t="b">
         <v>0</v>
       </c>
-      <c r="AI4" t="inlineStr">
-        <is>
-          <t>luckig gammal fjällgranskog, myrnära</t>
+      <c r="AJ4" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK4" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AN4" t="n">
@@ -1040,18 +996,23 @@
       </c>
       <c r="AO4" t="inlineStr">
         <is>
-          <t>1 substratenheter # grov granhögstubbe</t>
+          <t>1 substratenheter # Picea abies</t>
+        </is>
+      </c>
+      <c r="AS4" t="inlineStr">
+        <is>
+          <t>Anders Nordin</t>
         </is>
       </c>
       <c r="AT4" t="inlineStr"/>
       <c r="AW4" t="inlineStr">
         <is>
-          <t>Magnus Andersson</t>
+          <t>Magnus Johansson</t>
         </is>
       </c>
       <c r="AX4" t="inlineStr">
         <is>
-          <t>Magnus Andersson</t>
+          <t>Magnus Johansson</t>
         </is>
       </c>
       <c r="AY4" t="inlineStr">
@@ -1062,15 +1023,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>16895878</v>
+        <v>16895867</v>
       </c>
       <c r="B5" t="n">
-        <v>77668</v>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91923</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1078,34 +1034,34 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>1249</v>
+        <v>1204</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Norsk näverlav</t>
+          <t>Gränsticka</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Platismatia norvegica</t>
+          <t>Phellopilus nigrolimitatus</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Lynge) W.L.Culb. &amp; C.F.Culb.</t>
+          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
-          <t>Mosätern, NO om, Jmt</t>
+          <t>Övre Flohalsarna, ca 1 km SO Rörtjärnen, Jmt</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>449152.1871393301</v>
+        <v>449491</v>
       </c>
       <c r="R5" t="n">
-        <v>7171310.029633602</v>
+        <v>7170067</v>
       </c>
       <c r="S5" t="n">
         <v>25</v>
@@ -1135,21 +1091,11 @@
           <t>2014-07-01</t>
         </is>
       </c>
-      <c r="Z5" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA5" t="inlineStr">
         <is>
           <t>2014-07-01</t>
         </is>
       </c>
-      <c r="AB5" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AD5" t="b">
         <v>0</v>
       </c>
@@ -1161,15 +1107,15 @@
       </c>
       <c r="AI5" t="inlineStr">
         <is>
-          <t>luckig gammal fjällgranskog</t>
+          <t>luckig gammal fjällgranskog, myrnära</t>
         </is>
       </c>
       <c r="AN5" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="AO5" t="inlineStr">
         <is>
-          <t>5 substratenheter # döda grangrenar på gamla granar</t>
+          <t>2 substratenheter # gamla granlågor</t>
         </is>
       </c>
       <c r="AT5" t="inlineStr"/>
@@ -1191,15 +1137,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>16895868</v>
+        <v>16895874</v>
       </c>
       <c r="B6" t="n">
-        <v>77668</v>
-      </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91923</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1207,34 +1148,34 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>1249</v>
+        <v>1204</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Norsk näverlav</t>
+          <t>Gränsticka</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Platismatia norvegica</t>
+          <t>Phellopilus nigrolimitatus</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Lynge) W.L.Culb. &amp; C.F.Culb.</t>
+          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
-          <t>Övre Flohalsarna, ca 1 km SO Rörtjärnen, Jmt</t>
+          <t>Övre Flohalsarna, ca 1 km Ö om Rörtjärnen, Jmt</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>449399.2993477065</v>
+        <v>448976</v>
       </c>
       <c r="R6" t="n">
-        <v>7170334.342646328</v>
+        <v>7170810</v>
       </c>
       <c r="S6" t="n">
         <v>25</v>
@@ -1264,21 +1205,11 @@
           <t>2014-07-01</t>
         </is>
       </c>
-      <c r="Z6" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA6" t="inlineStr">
         <is>
           <t>2014-07-01</t>
         </is>
       </c>
-      <c r="AB6" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AD6" t="b">
         <v>0</v>
       </c>
@@ -1290,15 +1221,15 @@
       </c>
       <c r="AI6" t="inlineStr">
         <is>
-          <t>luckig, björkrik fjällgranskog, myrnära</t>
+          <t>luckig gammal fjällgranskog, myrnära</t>
         </is>
       </c>
       <c r="AN6" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="AO6" t="inlineStr">
         <is>
-          <t>2 substratenheter # grenar på 150-200-åriga granar</t>
+          <t>1 substratenheter # grov gammal granlåga</t>
         </is>
       </c>
       <c r="AT6" t="inlineStr"/>
@@ -1320,19 +1251,14 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>16895874</v>
+        <v>16895879</v>
       </c>
       <c r="B7" t="n">
-        <v>89406</v>
-      </c>
-      <c r="C7" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91923</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E7" t="n">
@@ -1356,14 +1282,14 @@
       <c r="I7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
-          <t>Övre Flohalsarna, ca 1 km Ö om Rörtjärnen, Jmt</t>
+          <t>Mosätern, NO om, Jmt</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>448975.5809481511</v>
+        <v>449183</v>
       </c>
       <c r="R7" t="n">
-        <v>7170809.909726117</v>
+        <v>7171376</v>
       </c>
       <c r="S7" t="n">
         <v>25</v>
@@ -1393,21 +1319,11 @@
           <t>2014-07-01</t>
         </is>
       </c>
-      <c r="Z7" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA7" t="inlineStr">
         <is>
           <t>2014-07-01</t>
         </is>
       </c>
-      <c r="AB7" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AD7" t="b">
         <v>0</v>
       </c>
@@ -1419,7 +1335,7 @@
       </c>
       <c r="AI7" t="inlineStr">
         <is>
-          <t>luckig gammal fjällgranskog, myrnära</t>
+          <t>luckig, björkrik fjällgranskog</t>
         </is>
       </c>
       <c r="AN7" t="n">
@@ -1449,50 +1365,45 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>16895877</v>
+        <v>16895881</v>
       </c>
       <c r="B8" t="n">
-        <v>94121</v>
-      </c>
-      <c r="C8" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91923</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>53</v>
+        <v>1204</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Vedtrappmossa</t>
+          <t>Gränsticka</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Crossocalyx hellerianus</t>
+          <t>Phellopilus nigrolimitatus</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Nees ex Lindenb.) Meyl.</t>
+          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
-          <t>Mosätern, Ö om, Jmt</t>
+          <t>Mosätern, N om, Jmt</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>449235.5839933903</v>
+        <v>448799</v>
       </c>
       <c r="R8" t="n">
-        <v>7171192.077653565</v>
+        <v>7171304</v>
       </c>
       <c r="S8" t="n">
         <v>25</v>
@@ -1522,19 +1433,9 @@
           <t>2014-07-01</t>
         </is>
       </c>
-      <c r="Z8" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA8" t="inlineStr">
         <is>
           <t>2014-07-01</t>
-        </is>
-      </c>
-      <c r="AB8" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1556,7 +1457,7 @@
       </c>
       <c r="AO8" t="inlineStr">
         <is>
-          <t>1 substratenheter # gammal granlåga, murken ved</t>
+          <t>1 substratenheter # grov gammal granlåga</t>
         </is>
       </c>
       <c r="AT8" t="inlineStr"/>
@@ -1581,12 +1482,7 @@
         <v>16895864</v>
       </c>
       <c r="B9" t="n">
-        <v>77668</v>
-      </c>
-      <c r="C9" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79486</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1618,10 +1514,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>449139.9164449496</v>
+        <v>449140</v>
       </c>
       <c r="R9" t="n">
-        <v>7169736.404673791</v>
+        <v>7169736</v>
       </c>
       <c r="S9" t="n">
         <v>25</v>
@@ -1651,19 +1547,9 @@
           <t>2014-07-01</t>
         </is>
       </c>
-      <c r="Z9" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA9" t="inlineStr">
         <is>
           <t>2014-07-01</t>
-        </is>
-      </c>
-      <c r="AB9" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1707,50 +1593,45 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>16895879</v>
+        <v>16895866</v>
       </c>
       <c r="B10" t="n">
-        <v>89406</v>
-      </c>
-      <c r="C10" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79486</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>1204</v>
+        <v>1249</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Gränsticka</t>
+          <t>Norsk näverlav</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Phellopilus nigrolimitatus</t>
+          <t>Platismatia norvegica</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
+          <t>(Lynge) W.L.Culb. &amp; C.F.Culb.</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
       <c r="P10" t="inlineStr">
         <is>
-          <t>Mosätern, NO om, Jmt</t>
+          <t>Övre Flohalsarna, ca 1 km SO Rörtjärnen, Jmt</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>449183.3321592438</v>
+        <v>449491</v>
       </c>
       <c r="R10" t="n">
-        <v>7171376.350578475</v>
+        <v>7170058</v>
       </c>
       <c r="S10" t="n">
         <v>25</v>
@@ -1780,21 +1661,11 @@
           <t>2014-07-01</t>
         </is>
       </c>
-      <c r="Z10" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA10" t="inlineStr">
         <is>
           <t>2014-07-01</t>
         </is>
       </c>
-      <c r="AB10" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AD10" t="b">
         <v>0</v>
       </c>
@@ -1806,15 +1677,12 @@
       </c>
       <c r="AI10" t="inlineStr">
         <is>
-          <t>luckig, björkrik fjällgranskog</t>
-        </is>
-      </c>
-      <c r="AN10" t="n">
-        <v>1</v>
+          <t>luckig gammal fjällgranskog, myrnära</t>
+        </is>
       </c>
       <c r="AO10" t="inlineStr">
         <is>
-          <t>1 substratenheter # grov gammal granlåga</t>
+          <t>tämligen allmän på grenar på gamla granar</t>
         </is>
       </c>
       <c r="AT10" t="inlineStr"/>
@@ -1836,37 +1704,32 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>16895867</v>
+        <v>16895868</v>
       </c>
       <c r="B11" t="n">
-        <v>89406</v>
-      </c>
-      <c r="C11" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79486</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>1204</v>
+        <v>1249</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Gränsticka</t>
+          <t>Norsk näverlav</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Phellopilus nigrolimitatus</t>
+          <t>Platismatia norvegica</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
+          <t>(Lynge) W.L.Culb. &amp; C.F.Culb.</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
@@ -1876,10 +1739,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>449490.5502878522</v>
+        <v>449399</v>
       </c>
       <c r="R11" t="n">
-        <v>7170067.486529554</v>
+        <v>7170334</v>
       </c>
       <c r="S11" t="n">
         <v>25</v>
@@ -1909,21 +1772,11 @@
           <t>2014-07-01</t>
         </is>
       </c>
-      <c r="Z11" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA11" t="inlineStr">
         <is>
           <t>2014-07-01</t>
         </is>
       </c>
-      <c r="AB11" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AD11" t="b">
         <v>0</v>
       </c>
@@ -1935,7 +1788,7 @@
       </c>
       <c r="AI11" t="inlineStr">
         <is>
-          <t>luckig gammal fjällgranskog, myrnära</t>
+          <t>luckig, björkrik fjällgranskog, myrnära</t>
         </is>
       </c>
       <c r="AN11" t="n">
@@ -1943,7 +1796,7 @@
       </c>
       <c r="AO11" t="inlineStr">
         <is>
-          <t>2 substratenheter # gamla granlågor</t>
+          <t>2 substratenheter # grenar på 150-200-åriga granar</t>
         </is>
       </c>
       <c r="AT11" t="inlineStr"/>
@@ -1965,50 +1818,45 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>16895881</v>
+        <v>16895869</v>
       </c>
       <c r="B12" t="n">
-        <v>89406</v>
-      </c>
-      <c r="C12" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79486</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>1204</v>
+        <v>1249</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Gränsticka</t>
+          <t>Norsk näverlav</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Phellopilus nigrolimitatus</t>
+          <t>Platismatia norvegica</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
+          <t>(Lynge) W.L.Culb. &amp; C.F.Culb.</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
       <c r="P12" t="inlineStr">
         <is>
-          <t>Mosätern, N om, Jmt</t>
+          <t>Övre Flohalsarna, ca 1,5 km Ö om Rörtjärnen, Jmt</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>448799.0070646548</v>
+        <v>449835</v>
       </c>
       <c r="R12" t="n">
-        <v>7171304.414421</v>
+        <v>7170700</v>
       </c>
       <c r="S12" t="n">
         <v>25</v>
@@ -2038,21 +1886,11 @@
           <t>2014-07-01</t>
         </is>
       </c>
-      <c r="Z12" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA12" t="inlineStr">
         <is>
           <t>2014-07-01</t>
         </is>
       </c>
-      <c r="AB12" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AD12" t="b">
         <v>0</v>
       </c>
@@ -2064,7 +1902,7 @@
       </c>
       <c r="AI12" t="inlineStr">
         <is>
-          <t>luckig, björkrik fjällgranskog</t>
+          <t>luckig, björkrik fjällgranskog, myrnära</t>
         </is>
       </c>
       <c r="AN12" t="n">
@@ -2072,7 +1910,7 @@
       </c>
       <c r="AO12" t="inlineStr">
         <is>
-          <t>1 substratenheter # grov gammal granlåga</t>
+          <t>1 substratenheter # stammen på gammal rönn</t>
         </is>
       </c>
       <c r="AT12" t="inlineStr"/>
@@ -2097,12 +1935,7 @@
         <v>16895872</v>
       </c>
       <c r="B13" t="n">
-        <v>77668</v>
-      </c>
-      <c r="C13" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79486</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -2134,10 +1967,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>449392.1534850246</v>
+        <v>449392</v>
       </c>
       <c r="R13" t="n">
-        <v>7170985.050578158</v>
+        <v>7170985</v>
       </c>
       <c r="S13" t="n">
         <v>25</v>
@@ -2167,19 +2000,9 @@
           <t>2014-07-01</t>
         </is>
       </c>
-      <c r="Z13" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA13" t="inlineStr">
         <is>
           <t>2014-07-01</t>
-        </is>
-      </c>
-      <c r="AB13" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -2223,50 +2046,45 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>16895865</v>
+        <v>16895873</v>
       </c>
       <c r="B14" t="n">
-        <v>73693</v>
-      </c>
-      <c r="C14" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79486</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>6440</v>
+        <v>1249</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Norsk näverlav</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Platismatia norvegica</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(Lynge) W.L.Culb. &amp; C.F.Culb.</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
       <c r="P14" t="inlineStr">
         <is>
-          <t>Övre Flohalsarna, ca 1 km SO Rörtjärnen, Jmt</t>
+          <t>Övre Flohalsarna, ca 1,5 km Ö om Rörtjärnen, Jmt</t>
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>449247.050219873</v>
+        <v>449443</v>
       </c>
       <c r="R14" t="n">
-        <v>7169879.509281839</v>
+        <v>7170680</v>
       </c>
       <c r="S14" t="n">
         <v>25</v>
@@ -2296,21 +2114,11 @@
           <t>2014-07-01</t>
         </is>
       </c>
-      <c r="Z14" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA14" t="inlineStr">
         <is>
           <t>2014-07-01</t>
         </is>
       </c>
-      <c r="AB14" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AD14" t="b">
         <v>0</v>
       </c>
@@ -2322,12 +2130,15 @@
       </c>
       <c r="AI14" t="inlineStr">
         <is>
-          <t>luckig gammal fjällgranskog</t>
-        </is>
+          <t>luckig gammal fjällgranskog, myrnära</t>
+        </is>
+      </c>
+      <c r="AN14" t="n">
+        <v>1</v>
       </c>
       <c r="AO14" t="inlineStr">
         <is>
-          <t>allmänt spridd på stammarna av 160-200-åriga granar</t>
+          <t>1 substratenheter # näver på grov, lutande björkhögstubbe</t>
         </is>
       </c>
       <c r="AT14" t="inlineStr"/>
@@ -2349,15 +2160,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>16895866</v>
+        <v>16895875</v>
       </c>
       <c r="B15" t="n">
-        <v>77668</v>
-      </c>
-      <c r="C15" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79486</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2385,14 +2191,14 @@
       <c r="I15" t="inlineStr"/>
       <c r="P15" t="inlineStr">
         <is>
-          <t>Övre Flohalsarna, ca 1 km SO Rörtjärnen, Jmt</t>
+          <t>Mosätern, Ö om, Jmt</t>
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>449490.8149566256</v>
+        <v>449263</v>
       </c>
       <c r="R15" t="n">
-        <v>7170057.622786808</v>
+        <v>7171067</v>
       </c>
       <c r="S15" t="n">
         <v>25</v>
@@ -2422,21 +2228,11 @@
           <t>2014-07-01</t>
         </is>
       </c>
-      <c r="Z15" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA15" t="inlineStr">
         <is>
           <t>2014-07-01</t>
         </is>
       </c>
-      <c r="AB15" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AD15" t="b">
         <v>0</v>
       </c>
@@ -2448,12 +2244,15 @@
       </c>
       <c r="AI15" t="inlineStr">
         <is>
-          <t>luckig gammal fjällgranskog, myrnära</t>
-        </is>
+          <t>luckig gammal fjällgranskog</t>
+        </is>
+      </c>
+      <c r="AN15" t="n">
+        <v>1</v>
       </c>
       <c r="AO15" t="inlineStr">
         <is>
-          <t>tämligen allmän på grenar på gamla granar</t>
+          <t>1 substratenheter # död grangren på gammal gran</t>
         </is>
       </c>
       <c r="AT15" t="inlineStr"/>
@@ -2475,15 +2274,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>16895875</v>
+        <v>16895878</v>
       </c>
       <c r="B16" t="n">
-        <v>77668</v>
-      </c>
-      <c r="C16" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79486</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2511,14 +2305,14 @@
       <c r="I16" t="inlineStr"/>
       <c r="P16" t="inlineStr">
         <is>
-          <t>Mosätern, Ö om, Jmt</t>
+          <t>Mosätern, NO om, Jmt</t>
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>449263.096811696</v>
+        <v>449152</v>
       </c>
       <c r="R16" t="n">
-        <v>7171067.34638738</v>
+        <v>7171310</v>
       </c>
       <c r="S16" t="n">
         <v>25</v>
@@ -2548,21 +2342,11 @@
           <t>2014-07-01</t>
         </is>
       </c>
-      <c r="Z16" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA16" t="inlineStr">
         <is>
           <t>2014-07-01</t>
         </is>
       </c>
-      <c r="AB16" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AD16" t="b">
         <v>0</v>
       </c>
@@ -2578,11 +2362,11 @@
         </is>
       </c>
       <c r="AN16" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="AO16" t="inlineStr">
         <is>
-          <t>1 substratenheter # död grangren på gammal gran</t>
+          <t>5 substratenheter # döda grangrenar på gamla granar</t>
         </is>
       </c>
       <c r="AT16" t="inlineStr"/>
@@ -2604,15 +2388,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>16895873</v>
+        <v>16895880</v>
       </c>
       <c r="B17" t="n">
-        <v>77668</v>
-      </c>
-      <c r="C17" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79486</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2640,14 +2419,14 @@
       <c r="I17" t="inlineStr"/>
       <c r="P17" t="inlineStr">
         <is>
-          <t>Övre Flohalsarna, ca 1,5 km Ö om Rörtjärnen, Jmt</t>
+          <t>Mosätern, N om, Jmt</t>
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>449442.8364162811</v>
+        <v>448996</v>
       </c>
       <c r="R17" t="n">
-        <v>7170679.927399937</v>
+        <v>7171334</v>
       </c>
       <c r="S17" t="n">
         <v>25</v>
@@ -2677,21 +2456,11 @@
           <t>2014-07-01</t>
         </is>
       </c>
-      <c r="Z17" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA17" t="inlineStr">
         <is>
           <t>2014-07-01</t>
         </is>
       </c>
-      <c r="AB17" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AD17" t="b">
         <v>0</v>
       </c>
@@ -2703,15 +2472,15 @@
       </c>
       <c r="AI17" t="inlineStr">
         <is>
-          <t>luckig gammal fjällgranskog, myrnära</t>
+          <t>luckig gammal fjällgranskog</t>
         </is>
       </c>
       <c r="AN17" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="AO17" t="inlineStr">
         <is>
-          <t>1 substratenheter # näver på grov, lutande björkhögstubbe</t>
+          <t>5 substratenheter # döda grangrenar på gamla granar</t>
         </is>
       </c>
       <c r="AT17" t="inlineStr"/>
@@ -2733,15 +2502,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>17225481</v>
+        <v>17225480</v>
       </c>
       <c r="B18" t="n">
-        <v>77668</v>
-      </c>
-      <c r="C18" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79486</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2773,13 +2537,13 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>448343.5007146247</v>
+        <v>448645</v>
       </c>
       <c r="R18" t="n">
-        <v>7169651.277689694</v>
+        <v>7169639</v>
       </c>
       <c r="S18" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T18" t="inlineStr">
         <is>
@@ -2806,21 +2570,11 @@
           <t>2014-07-18</t>
         </is>
       </c>
-      <c r="Z18" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA18" t="inlineStr">
         <is>
           <t>2014-07-18</t>
         </is>
       </c>
-      <c r="AB18" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AD18" t="b">
         <v>0</v>
       </c>
@@ -2841,11 +2595,11 @@
         </is>
       </c>
       <c r="AN18" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="AO18" t="inlineStr">
         <is>
-          <t>2 substratenheter # Picea abies</t>
+          <t>1 substratenheter # Picea abies</t>
         </is>
       </c>
       <c r="AT18" t="inlineStr"/>
@@ -2867,15 +2621,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>17225480</v>
+        <v>17225481</v>
       </c>
       <c r="B19" t="n">
-        <v>77668</v>
-      </c>
-      <c r="C19" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79486</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2907,13 +2656,13 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>448644.630458977</v>
+        <v>448344</v>
       </c>
       <c r="R19" t="n">
-        <v>7169638.868187833</v>
+        <v>7169651</v>
       </c>
       <c r="S19" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T19" t="inlineStr">
         <is>
@@ -2940,21 +2689,11 @@
           <t>2014-07-18</t>
         </is>
       </c>
-      <c r="Z19" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA19" t="inlineStr">
         <is>
           <t>2014-07-18</t>
         </is>
       </c>
-      <c r="AB19" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AD19" t="b">
         <v>0</v>
       </c>
@@ -2975,11 +2714,11 @@
         </is>
       </c>
       <c r="AN19" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AO19" t="inlineStr">
         <is>
-          <t>1 substratenheter # Picea abies</t>
+          <t>2 substratenheter # Picea abies</t>
         </is>
       </c>
       <c r="AT19" t="inlineStr"/>
@@ -3004,12 +2743,7 @@
         <v>17225483</v>
       </c>
       <c r="B20" t="n">
-        <v>77668</v>
-      </c>
-      <c r="C20" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79486</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -3041,10 +2775,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>448349.7665656545</v>
+        <v>448350</v>
       </c>
       <c r="R20" t="n">
-        <v>7169691.471229592</v>
+        <v>7169691</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -3074,19 +2808,9 @@
           <t>2014-07-18</t>
         </is>
       </c>
-      <c r="Z20" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA20" t="inlineStr">
         <is>
           <t>2014-07-18</t>
-        </is>
-      </c>
-      <c r="AB20" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -3135,53 +2859,48 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>16895870</v>
+        <v>17225485</v>
       </c>
       <c r="B21" t="n">
-        <v>94764</v>
-      </c>
-      <c r="C21" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79486</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>2326</v>
+        <v>1249</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Vanlig rörsvepemossa</t>
+          <t>Norsk näverlav</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Liochlaena lanceolata</t>
+          <t>Platismatia norvegica</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>Nees</t>
+          <t>(Lynge) W.L.Culb. &amp; C.F.Culb.</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
       <c r="P21" t="inlineStr">
         <is>
-          <t>Övre Flohalsarna, ca 1,5 km Ö om Rörtjärnen, Jmt</t>
+          <t>Mobäcken, Jmt</t>
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>449805.8680468608</v>
+        <v>448388</v>
       </c>
       <c r="R21" t="n">
-        <v>7170680.315228821</v>
+        <v>7169578</v>
       </c>
       <c r="S21" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T21" t="inlineStr">
         <is>
@@ -3205,22 +2924,12 @@
       </c>
       <c r="Y21" t="inlineStr">
         <is>
-          <t>2014-07-01</t>
-        </is>
-      </c>
-      <c r="Z21" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2014-07-18</t>
         </is>
       </c>
       <c r="AA21" t="inlineStr">
         <is>
-          <t>2014-07-01</t>
-        </is>
-      </c>
-      <c r="AB21" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2014-07-18</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -3232,9 +2941,14 @@
       <c r="AG21" t="b">
         <v>0</v>
       </c>
-      <c r="AI21" t="inlineStr">
-        <is>
-          <t>luckig, björkrik fjällgranskog, myrnära</t>
+      <c r="AJ21" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK21" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AN21" t="n">
@@ -3242,18 +2956,18 @@
       </c>
       <c r="AO21" t="inlineStr">
         <is>
-          <t>1 substratenheter # gammal granlåga, murken ved</t>
+          <t>1 substratenheter # Picea abies</t>
         </is>
       </c>
       <c r="AT21" t="inlineStr"/>
       <c r="AW21" t="inlineStr">
         <is>
-          <t>Magnus Andersson</t>
+          <t>Magnus Johansson</t>
         </is>
       </c>
       <c r="AX21" t="inlineStr">
         <is>
-          <t>Magnus Andersson</t>
+          <t>Magnus Johansson</t>
         </is>
       </c>
       <c r="AY21" t="inlineStr">
@@ -3264,15 +2978,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>16895876</v>
+        <v>16895870</v>
       </c>
       <c r="B22" t="n">
-        <v>94764</v>
-      </c>
-      <c r="C22" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>97678</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -3300,14 +3009,14 @@
       <c r="I22" t="inlineStr"/>
       <c r="P22" t="inlineStr">
         <is>
-          <t>Mosätern, Ö om, Jmt</t>
+          <t>Övre Flohalsarna, ca 1,5 km Ö om Rörtjärnen, Jmt</t>
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>449235.5839933903</v>
+        <v>449806</v>
       </c>
       <c r="R22" t="n">
-        <v>7171192.077653565</v>
+        <v>7170680</v>
       </c>
       <c r="S22" t="n">
         <v>25</v>
@@ -3337,21 +3046,11 @@
           <t>2014-07-01</t>
         </is>
       </c>
-      <c r="Z22" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA22" t="inlineStr">
         <is>
           <t>2014-07-01</t>
         </is>
       </c>
-      <c r="AB22" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AD22" t="b">
         <v>0</v>
       </c>
@@ -3363,7 +3062,7 @@
       </c>
       <c r="AI22" t="inlineStr">
         <is>
-          <t>luckig, björkrik fjällgranskog</t>
+          <t>luckig, björkrik fjällgranskog, myrnära</t>
         </is>
       </c>
       <c r="AN22" t="n">
@@ -3393,56 +3092,48 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>17225482</v>
+        <v>16895876</v>
       </c>
       <c r="B23" t="n">
-        <v>76863</v>
-      </c>
-      <c r="C23" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>97678</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E23" t="n">
-        <v>498</v>
+        <v>2326</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Liten sotlav</t>
+          <t>Vanlig rörsvepemossa</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Acolium karelicum</t>
+          <t>Liochlaena lanceolata</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Vain.) M.Prieto &amp; Wedin</t>
+          <t>Nees</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
-      <c r="J23" t="inlineStr"/>
-      <c r="K23" t="inlineStr"/>
-      <c r="N23" t="inlineStr"/>
       <c r="P23" t="inlineStr">
         <is>
-          <t>Mobäcken, Jmt</t>
+          <t>Mosätern, Ö om, Jmt</t>
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>448349.7665656545</v>
+        <v>449236</v>
       </c>
       <c r="R23" t="n">
-        <v>7169691.471229592</v>
+        <v>7171192</v>
       </c>
       <c r="S23" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T23" t="inlineStr">
         <is>
@@ -3466,27 +3157,12 @@
       </c>
       <c r="Y23" t="inlineStr">
         <is>
-          <t>2014-07-18</t>
-        </is>
-      </c>
-      <c r="Z23" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2014-07-01</t>
         </is>
       </c>
       <c r="AA23" t="inlineStr">
         <is>
-          <t>2014-07-18</t>
-        </is>
-      </c>
-      <c r="AB23" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
-      <c r="AC23" t="inlineStr">
-        <is>
-          <t>Artbestämd av Anders Nordin</t>
+          <t>2014-07-01</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -3495,18 +3171,12 @@
       <c r="AE23" t="b">
         <v>0</v>
       </c>
-      <c r="AF23" t="inlineStr"/>
       <c r="AG23" t="b">
         <v>0</v>
       </c>
-      <c r="AJ23" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK23" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
+      <c r="AI23" t="inlineStr">
+        <is>
+          <t>luckig, björkrik fjällgranskog</t>
         </is>
       </c>
       <c r="AN23" t="n">
@@ -3514,26 +3184,246 @@
       </c>
       <c r="AO23" t="inlineStr">
         <is>
-          <t>1 substratenheter # Picea abies</t>
-        </is>
-      </c>
-      <c r="AS23" t="inlineStr">
-        <is>
-          <t>Anders Nordin</t>
+          <t>1 substratenheter # gammal granlåga, murken ved</t>
         </is>
       </c>
       <c r="AT23" t="inlineStr"/>
       <c r="AW23" t="inlineStr">
         <is>
-          <t>Magnus Johansson</t>
+          <t>Magnus Andersson</t>
         </is>
       </c>
       <c r="AX23" t="inlineStr">
         <is>
-          <t>Magnus Johansson</t>
+          <t>Magnus Andersson</t>
         </is>
       </c>
       <c r="AY23" t="inlineStr">
+        <is>
+          <t>SCA Skog Naturvärdesinventering</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="n">
+        <v>16895871</v>
+      </c>
+      <c r="B24" t="n">
+        <v>92632</v>
+      </c>
+      <c r="D24" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E24" t="n">
+        <v>3298</v>
+      </c>
+      <c r="F24" t="inlineStr">
+        <is>
+          <t>Trådticka</t>
+        </is>
+      </c>
+      <c r="G24" t="inlineStr">
+        <is>
+          <t>Climacocystis borealis</t>
+        </is>
+      </c>
+      <c r="H24" t="inlineStr">
+        <is>
+          <t>(Fr.) Kotl. &amp; Pouzar</t>
+        </is>
+      </c>
+      <c r="I24" t="inlineStr"/>
+      <c r="P24" t="inlineStr">
+        <is>
+          <t>Övre Flohalsarna, ca 1,5 km Ö om Rörtjärnen, Jmt</t>
+        </is>
+      </c>
+      <c r="Q24" t="n">
+        <v>449402</v>
+      </c>
+      <c r="R24" t="n">
+        <v>7170995</v>
+      </c>
+      <c r="S24" t="n">
+        <v>25</v>
+      </c>
+      <c r="T24" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U24" t="inlineStr">
+        <is>
+          <t>Strömsund</t>
+        </is>
+      </c>
+      <c r="V24" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W24" t="inlineStr">
+        <is>
+          <t>Frostviken</t>
+        </is>
+      </c>
+      <c r="Y24" t="inlineStr">
+        <is>
+          <t>2014-07-01</t>
+        </is>
+      </c>
+      <c r="AA24" t="inlineStr">
+        <is>
+          <t>2014-07-01</t>
+        </is>
+      </c>
+      <c r="AD24" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE24" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG24" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI24" t="inlineStr">
+        <is>
+          <t>luckig gammal fjällgranskog, myrnära</t>
+        </is>
+      </c>
+      <c r="AN24" t="n">
+        <v>1</v>
+      </c>
+      <c r="AO24" t="inlineStr">
+        <is>
+          <t>1 substratenheter # grov granhögstubbe</t>
+        </is>
+      </c>
+      <c r="AT24" t="inlineStr"/>
+      <c r="AW24" t="inlineStr">
+        <is>
+          <t>Magnus Andersson</t>
+        </is>
+      </c>
+      <c r="AX24" t="inlineStr">
+        <is>
+          <t>Magnus Andersson</t>
+        </is>
+      </c>
+      <c r="AY24" t="inlineStr">
+        <is>
+          <t>SCA Skog Naturvärdesinventering</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="n">
+        <v>16895865</v>
+      </c>
+      <c r="B25" t="n">
+        <v>83307</v>
+      </c>
+      <c r="D25" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E25" t="n">
+        <v>6440</v>
+      </c>
+      <c r="F25" t="inlineStr">
+        <is>
+          <t>Vitgrynig nållav</t>
+        </is>
+      </c>
+      <c r="G25" t="inlineStr">
+        <is>
+          <t>Chaenotheca subroscida</t>
+        </is>
+      </c>
+      <c r="H25" t="inlineStr">
+        <is>
+          <t>(Eitner) Zahlbr.</t>
+        </is>
+      </c>
+      <c r="I25" t="inlineStr"/>
+      <c r="P25" t="inlineStr">
+        <is>
+          <t>Övre Flohalsarna, ca 1 km SO Rörtjärnen, Jmt</t>
+        </is>
+      </c>
+      <c r="Q25" t="n">
+        <v>449247</v>
+      </c>
+      <c r="R25" t="n">
+        <v>7169880</v>
+      </c>
+      <c r="S25" t="n">
+        <v>25</v>
+      </c>
+      <c r="T25" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U25" t="inlineStr">
+        <is>
+          <t>Strömsund</t>
+        </is>
+      </c>
+      <c r="V25" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W25" t="inlineStr">
+        <is>
+          <t>Frostviken</t>
+        </is>
+      </c>
+      <c r="Y25" t="inlineStr">
+        <is>
+          <t>2014-07-01</t>
+        </is>
+      </c>
+      <c r="AA25" t="inlineStr">
+        <is>
+          <t>2014-07-01</t>
+        </is>
+      </c>
+      <c r="AD25" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE25" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG25" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI25" t="inlineStr">
+        <is>
+          <t>luckig gammal fjällgranskog</t>
+        </is>
+      </c>
+      <c r="AO25" t="inlineStr">
+        <is>
+          <t>allmänt spridd på stammarna av 160-200-åriga granar</t>
+        </is>
+      </c>
+      <c r="AT25" t="inlineStr"/>
+      <c r="AW25" t="inlineStr">
+        <is>
+          <t>Magnus Andersson</t>
+        </is>
+      </c>
+      <c r="AX25" t="inlineStr">
+        <is>
+          <t>Magnus Andersson</t>
+        </is>
+      </c>
+      <c r="AY25" t="inlineStr">
         <is>
           <t>SCA Skog Naturvärdesinventering</t>
         </is>

--- a/artfynd/A 63509-2021 artfynd.xlsx
+++ b/artfynd/A 63509-2021 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY25"/>
+  <dimension ref="A1:AZ25"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -670,6 +670,11 @@
       <c r="AY1" t="inlineStr">
         <is>
           <t>Projektnamn</t>
+        </is>
+      </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
         </is>
       </c>
     </row>
@@ -805,6 +810,11 @@
           <t>SCA Skog Naturvärdesinventering</t>
         </is>
       </c>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/17225482</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -924,6 +934,11 @@
           <t>SCA Skog Naturvärdesinventering</t>
         </is>
       </c>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/17225480</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -1043,6 +1058,11 @@
           <t>SCA Skog Naturvärdesinventering</t>
         </is>
       </c>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/17225481</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1162,6 +1182,11 @@
           <t>SCA Skog Naturvärdesinventering</t>
         </is>
       </c>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/17225483</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -1281,6 +1306,11 @@
           <t>SCA Skog Naturvärdesinventering</t>
         </is>
       </c>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/17225485</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -1395,6 +1425,11 @@
           <t>SCA Skog Naturvärdesinventering</t>
         </is>
       </c>
+      <c r="AZ7" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/16895874</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
@@ -1509,6 +1544,11 @@
           <t>SCA Skog Naturvärdesinventering</t>
         </is>
       </c>
+      <c r="AZ8" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/16895881</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
@@ -1621,6 +1661,11 @@
       <c r="AY9" t="inlineStr">
         <is>
           <t>SCA Skog Naturvärdesinventering</t>
+        </is>
+      </c>
+      <c r="AZ9" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/16895880</t>
         </is>
       </c>
     </row>
@@ -1724,6 +1769,11 @@
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
+      <c r="AZ10" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120189967</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
@@ -1838,6 +1888,11 @@
           <t>SCA Skog Naturvärdesinventering</t>
         </is>
       </c>
+      <c r="AZ11" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/16895867</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
@@ -1952,6 +2007,11 @@
           <t>SCA Skog Naturvärdesinventering</t>
         </is>
       </c>
+      <c r="AZ12" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/16895864</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
@@ -2063,6 +2123,11 @@
           <t>SCA Skog Naturvärdesinventering</t>
         </is>
       </c>
+      <c r="AZ13" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/16895866</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="n">
@@ -2174,6 +2239,11 @@
           <t>SCA Skog Naturvärdesinventering</t>
         </is>
       </c>
+      <c r="AZ14" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/16895865</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="n">
@@ -2288,6 +2358,11 @@
           <t>SCA Skog Naturvärdesinventering</t>
         </is>
       </c>
+      <c r="AZ15" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/16895877</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="n">
@@ -2402,6 +2477,11 @@
           <t>SCA Skog Naturvärdesinventering</t>
         </is>
       </c>
+      <c r="AZ16" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/16895879</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="n">
@@ -2516,6 +2596,11 @@
           <t>SCA Skog Naturvärdesinventering</t>
         </is>
       </c>
+      <c r="AZ17" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/16895868</t>
+        </is>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="n">
@@ -2630,6 +2715,11 @@
           <t>SCA Skog Naturvärdesinventering</t>
         </is>
       </c>
+      <c r="AZ18" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/16895869</t>
+        </is>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="n">
@@ -2744,6 +2834,11 @@
           <t>SCA Skog Naturvärdesinventering</t>
         </is>
       </c>
+      <c r="AZ19" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/16895872</t>
+        </is>
+      </c>
     </row>
     <row r="20">
       <c r="A20" t="n">
@@ -2858,6 +2953,11 @@
           <t>SCA Skog Naturvärdesinventering</t>
         </is>
       </c>
+      <c r="AZ20" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/16895873</t>
+        </is>
+      </c>
     </row>
     <row r="21">
       <c r="A21" t="n">
@@ -2972,6 +3072,11 @@
           <t>SCA Skog Naturvärdesinventering</t>
         </is>
       </c>
+      <c r="AZ21" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/16895875</t>
+        </is>
+      </c>
     </row>
     <row r="22">
       <c r="A22" t="n">
@@ -3086,6 +3191,11 @@
           <t>SCA Skog Naturvärdesinventering</t>
         </is>
       </c>
+      <c r="AZ22" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/16895878</t>
+        </is>
+      </c>
     </row>
     <row r="23">
       <c r="A23" t="n">
@@ -3200,6 +3310,11 @@
           <t>SCA Skog Naturvärdesinventering</t>
         </is>
       </c>
+      <c r="AZ23" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/16895870</t>
+        </is>
+      </c>
     </row>
     <row r="24">
       <c r="A24" t="n">
@@ -3314,6 +3429,11 @@
           <t>SCA Skog Naturvärdesinventering</t>
         </is>
       </c>
+      <c r="AZ24" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/16895876</t>
+        </is>
+      </c>
     </row>
     <row r="25">
       <c r="A25" t="n">
@@ -3428,8 +3548,39 @@
           <t>SCA Skog Naturvärdesinventering</t>
         </is>
       </c>
+      <c r="AZ25" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/16895871</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ7" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ8" r:id="rId7"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ9" r:id="rId8"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ10" r:id="rId9"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ11" r:id="rId10"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ12" r:id="rId11"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ13" r:id="rId12"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ14" r:id="rId13"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ15" r:id="rId14"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ16" r:id="rId15"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ17" r:id="rId16"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ18" r:id="rId17"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ19" r:id="rId18"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ20" r:id="rId19"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ21" r:id="rId20"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ22" r:id="rId21"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ23" r:id="rId22"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ24" r:id="rId23"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ25" r:id="rId24"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>